--- a/XLOOKUP_sales_analysis.xlsx
+++ b/XLOOKUP_sales_analysis.xlsx
@@ -8,22 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Angel\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3DDBBB-C8F6-4D1B-A90C-7C90509EF09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F3766F-3ECB-4A35-BF86-DD320E3930F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="5" r:id="rId1"/>
-    <sheet name="Products" sheetId="1" r:id="rId2"/>
-    <sheet name="Orders" sheetId="2" r:id="rId3"/>
-    <sheet name="Pivot Table" sheetId="3" r:id="rId4"/>
+    <sheet name="Products" sheetId="1" r:id="rId1"/>
+    <sheet name="Orders" sheetId="2" r:id="rId2"/>
+    <sheet name="Pivot Table" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Orders!$A$1:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Orders!$A$1:$I$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
   <si>
     <t>ProductID</t>
   </si>
@@ -126,51 +125,6 @@
   </si>
   <si>
     <t>Revenue</t>
-  </si>
-  <si>
-    <t>The main goal of this spreadsheet is to find items. I used a mix of XLOOKUP and PivotTables on this sample and the same method can be scaled to thousands of rows. I chose XLOOKUP because it highlights IDs that do not match any record in the Products sheet.</t>
-  </si>
-  <si>
-    <t>This sample has two sheets. The Products sheet includes product ID, name, category and price. The Orders sheet has Order ID, date, ProductID and quantity as the data. Product name, category, unit price, total and status are calculated columns. Most of these are built using XLOOKUP. The total is calculated with a formula that multiplies quantity by unit price.</t>
-  </si>
-  <si>
-    <t>XLOOKUP with "Not found"</t>
-  </si>
-  <si>
-    <t>Left-lookup by product name</t>
-  </si>
-  <si>
-    <t>Multicolumn spill</t>
-  </si>
-  <si>
-    <t>Total column (Quantity × UnitPrice)</t>
-  </si>
-  <si>
-    <t>Status flag</t>
-  </si>
-  <si>
-    <t>PivotTable</t>
-  </si>
-  <si>
-    <t>While setting up XLOOKUP the lookup failed to find matches. The issue was that the Orders sheet showed P102 as the product ID but the actual value stored was 102 because I had applied a custom cell format that adds a "P" in front of numbers. The Products sheet stored the full text P102 so Excel compared a number, to text. Found no match. I discovered this by clicking the cell and checking the formula bar, which showed 102 of P102. I fixed it by adjusting the XLOOKUP formula to work with numbers and keeping the custom cell formatting.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GOAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DATA</t>
-  </si>
-  <si>
-    <t>TECHNIQUES</t>
-  </si>
-  <si>
-    <t>FINDINGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PROBLEM I SOLVED</t>
-  </si>
-  <si>
-    <t>The PivotTable groups data by category in columns and by date in rows. It shows revenue totals. Electronics made $3,150 out of the $3,980 total, which is about 79%. Two of the 12 orders used product IDs P999 and P110 which did not appear in the Products sheet. The Status column marked both as " product". All other orders show "OK". ![Orders with missing products flagged](orders_missing_flagged.png)</t>
   </si>
 </sst>
 </file>
@@ -184,7 +138,7 @@
     <numFmt numFmtId="165" formatCode="&quot;P&quot;###"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,20 +168,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -272,7 +212,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -280,15 +220,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -897,133 +828,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE36A27-F19D-4F15-87E4-BE6200D64322}">
-  <dimension ref="A2:A30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="100.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-    </row>
-    <row r="6" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-    </row>
-    <row r="8" spans="1:1" ht="63" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-    </row>
-    <row r="10" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-    </row>
-    <row r="12" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-    </row>
-    <row r="14" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
-    </row>
-    <row r="16" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-    </row>
-    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
-    </row>
-    <row r="20" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
-    </row>
-    <row r="22" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-    </row>
-    <row r="24" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-    </row>
-    <row r="26" spans="1:1" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-    </row>
-    <row r="28" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-    </row>
-    <row r="30" spans="1:1" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1036,198 +840,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="14" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
+      <c r="A2" s="8">
         <v>101</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="10">
         <v>850</v>
       </c>
-      <c r="F2" s="9" t="str">
+      <c r="F2" s="6" t="str">
         <f>B4</f>
         <v>Keyboard</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="8">
         <f>_xlfn.XLOOKUP(F2,$B$1:$B$9,$A$1:$A$9,"not found")</f>
         <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="8">
         <f>A2+1</f>
         <v>102</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="10">
         <v>25</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="8">
         <f t="shared" ref="G3:G9" si="0">_xlfn.XLOOKUP(F3,$B$1:$B$9,$A$1:$A$9,"not found")</f>
         <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
+      <c r="A4" s="8">
         <f t="shared" ref="A4:A9" si="1">A3+1</f>
         <v>103</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="10">
         <v>45</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="8">
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
+      <c r="A5" s="8">
         <f t="shared" si="1"/>
         <v>104</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="10">
         <v>220</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="8">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
+      <c r="A6" s="8">
         <f t="shared" si="1"/>
         <v>105</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="10">
         <v>310</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="8">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
+      <c r="A7" s="8">
         <f t="shared" si="1"/>
         <v>106</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="10">
         <v>180</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="11" t="str">
+      <c r="G7" s="8" t="str">
         <f t="shared" si="0"/>
         <v>not found</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
+      <c r="A8" s="8">
         <f t="shared" si="1"/>
         <v>107</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="10">
         <v>4</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="8">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="A9" s="8">
         <f t="shared" si="1"/>
         <v>108</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="10">
         <v>8</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="11" t="str">
+      <c r="G9" s="8" t="str">
         <f t="shared" si="0"/>
         <v>not found</v>
       </c>
@@ -1277,7 +1081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B39A56-ED26-4A39-82A9-01BAB67A314D}">
   <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1294,449 +1098,449 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
+      <c r="A2" s="6">
         <v>1001</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="7">
         <v>46266</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="8">
         <v>102</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="6">
         <v>3</v>
       </c>
-      <c r="E2" s="9" t="str">
+      <c r="E2" s="6" t="str">
         <f>_xlfn.XLOOKUP(C2,Products!$A$2:$A$9,Products!$B$2:$B$9,"Not found")</f>
         <v>Mouse</v>
       </c>
-      <c r="F2" s="9" t="str">
+      <c r="F2" s="6" t="str">
         <f>_xlfn.XLOOKUP(C2,Products!$A$2:$A$9,Products!$C$2:$C$9,"Not found")</f>
         <v>Electronics</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="9">
         <f>_xlfn.XLOOKUP(C2,Products!$A$2:$A$9,Products!$D$2:$D$9,"")</f>
         <v>25</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="10">
         <f>D2*G2</f>
         <v>75</v>
       </c>
-      <c r="I2" s="9" t="str">
+      <c r="I2" s="6" t="str">
         <f>IF(E2="NOT FOUND","Missing Product","OK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="6">
         <f>A2+1</f>
         <v>1002</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="7">
         <v>46266</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="8">
         <v>105</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="6">
         <v>1</v>
       </c>
-      <c r="E3" s="9" t="str">
+      <c r="E3" s="6" t="str">
         <f>_xlfn.XLOOKUP(C3,Products!$A$2:$A$9,Products!$B$2:$B$9,"Not found")</f>
         <v>Desk</v>
       </c>
-      <c r="F3" s="9" t="str">
+      <c r="F3" s="6" t="str">
         <f>_xlfn.XLOOKUP(C3,Products!$A$2:$A$9,Products!$C$2:$C$9,"Not found")</f>
         <v>Furniture</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="10">
         <f>_xlfn.XLOOKUP(C3,Products!$A$2:$A$9,Products!$D$2:$D$9,"")</f>
         <v>310</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="10">
         <f t="shared" ref="H3:H13" si="0">D3*G3</f>
         <v>310</v>
       </c>
-      <c r="I3" s="9" t="str">
+      <c r="I3" s="6" t="str">
         <f t="shared" ref="I3:I13" si="1">IF(E3="NOT FOUND","Missing Product","OK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+      <c r="A4" s="6">
         <f t="shared" ref="A4:A13" si="2">A3+1</f>
         <v>1003</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="7">
         <v>46267</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="8">
         <v>101</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="6">
         <v>2</v>
       </c>
-      <c r="E4" s="9" t="str">
+      <c r="E4" s="6" t="str">
         <f>_xlfn.XLOOKUP(C4,Products!$A$2:$A$9,Products!$B$2:$B$9,"Not found")</f>
         <v>Laptop</v>
       </c>
-      <c r="F4" s="9" t="str">
+      <c r="F4" s="6" t="str">
         <f>_xlfn.XLOOKUP(C4,Products!$A$2:$A$9,Products!$C$2:$C$9,"Not found")</f>
         <v>Electronics</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="10">
         <f>_xlfn.XLOOKUP(C4,Products!$A$2:$A$9,Products!$D$2:$D$9,"")</f>
         <v>850</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="10">
         <f t="shared" si="0"/>
         <v>1700</v>
       </c>
-      <c r="I4" s="9" t="str">
+      <c r="I4" s="6" t="str">
         <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+      <c r="A5" s="6">
         <f t="shared" si="2"/>
         <v>1004</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="7">
         <v>46268</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="8">
         <v>108</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="6">
         <v>10</v>
       </c>
-      <c r="E5" s="9" t="str">
+      <c r="E5" s="6" t="str">
         <f>_xlfn.XLOOKUP(C5,Products!$A$2:$A$9,Products!$B$2:$B$9,"Not found")</f>
         <v>Pen Pack</v>
       </c>
-      <c r="F5" s="9" t="str">
+      <c r="F5" s="6" t="str">
         <f>_xlfn.XLOOKUP(C5,Products!$A$2:$A$9,Products!$C$2:$C$9,"Not found")</f>
         <v>Stationery</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="10">
         <f>_xlfn.XLOOKUP(C5,Products!$A$2:$A$9,Products!$D$2:$D$9,"")</f>
         <v>8</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="10">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="I5" s="9" t="str">
+      <c r="I5" s="6" t="str">
         <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+      <c r="A6" s="6">
         <f t="shared" si="2"/>
         <v>1005</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <v>46268</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="8">
         <v>104</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="6">
         <v>1</v>
       </c>
-      <c r="E6" s="9" t="str">
+      <c r="E6" s="6" t="str">
         <f>_xlfn.XLOOKUP(C6,Products!$A$2:$A$9,Products!$B$2:$B$9,"Not found")</f>
         <v>Monitor</v>
       </c>
-      <c r="F6" s="9" t="str">
+      <c r="F6" s="6" t="str">
         <f>_xlfn.XLOOKUP(C6,Products!$A$2:$A$9,Products!$C$2:$C$9,"Not found")</f>
         <v>Electronics</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="10">
         <f>_xlfn.XLOOKUP(C6,Products!$A$2:$A$9,Products!$D$2:$D$9,"")</f>
         <v>220</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="10">
         <f t="shared" si="0"/>
         <v>220</v>
       </c>
-      <c r="I6" s="9" t="str">
+      <c r="I6" s="6" t="str">
         <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+      <c r="A7" s="6">
         <f t="shared" si="2"/>
         <v>1006</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <v>46269</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="8">
         <v>106</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="6">
         <v>2</v>
       </c>
-      <c r="E7" s="9" t="str">
+      <c r="E7" s="6" t="str">
         <f>_xlfn.XLOOKUP(C7,Products!$A$2:$A$9,Products!$B$2:$B$9,"Not found")</f>
         <v>Chair</v>
       </c>
-      <c r="F7" s="9" t="str">
+      <c r="F7" s="6" t="str">
         <f>_xlfn.XLOOKUP(C7,Products!$A$2:$A$9,Products!$C$2:$C$9,"Not found")</f>
         <v>Furniture</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="10">
         <f>_xlfn.XLOOKUP(C7,Products!$A$2:$A$9,Products!$D$2:$D$9,"")</f>
         <v>180</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="10">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="I7" s="9" t="str">
+      <c r="I7" s="6" t="str">
         <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+      <c r="A8" s="6">
         <f t="shared" si="2"/>
         <v>1007</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <v>46270</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="8">
         <v>103</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="6">
         <v>4</v>
       </c>
-      <c r="E8" s="9" t="str">
+      <c r="E8" s="6" t="str">
         <f>_xlfn.XLOOKUP(C8,Products!$A$2:$A$9,Products!$B$2:$B$9,"Not found")</f>
         <v>Keyboard</v>
       </c>
-      <c r="F8" s="9" t="str">
+      <c r="F8" s="6" t="str">
         <f>_xlfn.XLOOKUP(C8,Products!$A$2:$A$9,Products!$C$2:$C$9,"Not found")</f>
         <v>Electronics</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="10">
         <f>_xlfn.XLOOKUP(C8,Products!$A$2:$A$9,Products!$D$2:$D$9,"")</f>
         <v>45</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="10">
         <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="I8" s="9" t="str">
+      <c r="I8" s="6" t="str">
         <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+      <c r="A9" s="6">
         <f t="shared" si="2"/>
         <v>1008</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="7">
         <v>46270</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <v>999</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="6">
         <v>1</v>
       </c>
-      <c r="E9" s="9" t="str">
+      <c r="E9" s="6" t="str">
         <f>_xlfn.XLOOKUP(C9,Products!$A$2:$A$9,Products!$B$2:$B$9,"Not found")</f>
         <v>Not found</v>
       </c>
-      <c r="F9" s="9" t="str">
+      <c r="F9" s="6" t="str">
         <f>_xlfn.XLOOKUP(C9,Products!$A$2:$A$9,Products!$C$2:$C$9,"Not found")</f>
         <v>Not found</v>
       </c>
-      <c r="G9" s="13" t="str">
+      <c r="G9" s="10" t="str">
         <f>_xlfn.XLOOKUP(C9,Products!$A$2:$A$9,Products!$D$2:$D$9,"0")</f>
         <v>0</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="9" t="str">
+      <c r="I9" s="6" t="str">
         <f t="shared" si="1"/>
         <v>Missing Product</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
+      <c r="A10" s="6">
         <f t="shared" si="2"/>
         <v>1009</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="7">
         <v>46271</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="8">
         <v>107</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="6">
         <v>20</v>
       </c>
-      <c r="E10" s="9" t="str">
+      <c r="E10" s="6" t="str">
         <f>_xlfn.XLOOKUP(C10,Products!$A$2:$A$9,Products!$B$2:$B$9,"Not found")</f>
         <v>Notebook</v>
       </c>
-      <c r="F10" s="9" t="str">
+      <c r="F10" s="6" t="str">
         <f>_xlfn.XLOOKUP(C10,Products!$A$2:$A$9,Products!$C$2:$C$9,"Not found")</f>
         <v>Stationery</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="10">
         <f>_xlfn.XLOOKUP(C10,Products!$A$2:$A$9,Products!$D$2:$D$9,"")</f>
         <v>4</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="10">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="I10" s="9" t="str">
+      <c r="I10" s="6" t="str">
         <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
+      <c r="A11" s="6">
         <f t="shared" si="2"/>
         <v>1010</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="7">
         <v>46272</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="8">
         <v>101</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="6">
         <v>1</v>
       </c>
-      <c r="E11" s="9" t="str">
+      <c r="E11" s="6" t="str">
         <f>_xlfn.XLOOKUP(C11,Products!$A$2:$A$9,Products!$B$2:$B$9,"Not found")</f>
         <v>Laptop</v>
       </c>
-      <c r="F11" s="9" t="str">
+      <c r="F11" s="6" t="str">
         <f>_xlfn.XLOOKUP(C11,Products!$A$2:$A$9,Products!$C$2:$C$9,"Not found")</f>
         <v>Electronics</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="10">
         <f>_xlfn.XLOOKUP(C11,Products!$A$2:$A$9,Products!$D$2:$D$9,"")</f>
         <v>850</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="10">
         <f t="shared" si="0"/>
         <v>850</v>
       </c>
-      <c r="I11" s="9" t="str">
+      <c r="I11" s="6" t="str">
         <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
+      <c r="A12" s="6">
         <f t="shared" si="2"/>
         <v>1011</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="7">
         <v>46273</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="8">
         <v>102</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="6">
         <v>5</v>
       </c>
-      <c r="E12" s="9" t="str">
+      <c r="E12" s="6" t="str">
         <f>_xlfn.XLOOKUP(C12,Products!$A$2:$A$9,Products!$B$2:$B$9,"Not found")</f>
         <v>Mouse</v>
       </c>
-      <c r="F12" s="9" t="str">
+      <c r="F12" s="6" t="str">
         <f>_xlfn.XLOOKUP(C12,Products!$A$2:$A$9,Products!$C$2:$C$9,"Not found")</f>
         <v>Electronics</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="10">
         <f>_xlfn.XLOOKUP(C12,Products!$A$2:$A$9,Products!$D$2:$D$9,"")</f>
         <v>25</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="10">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="I12" s="9" t="str">
+      <c r="I12" s="6" t="str">
         <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
+      <c r="A13" s="6">
         <f t="shared" si="2"/>
         <v>1012</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="7">
         <v>46273</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="8">
         <v>110</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="6">
         <v>2</v>
       </c>
-      <c r="E13" s="9" t="str">
+      <c r="E13" s="6" t="str">
         <f>_xlfn.XLOOKUP(C13,Products!$A$2:$A$9,Products!$B$2:$B$9,"Not found")</f>
         <v>Not found</v>
       </c>
-      <c r="F13" s="9" t="str">
+      <c r="F13" s="6" t="str">
         <f>_xlfn.XLOOKUP(C13,Products!$A$2:$A$9,Products!$C$2:$C$9,"Not found")</f>
         <v>Not found</v>
       </c>
-      <c r="G13" s="13" t="str">
+      <c r="G13" s="10" t="str">
         <f>_xlfn.XLOOKUP(C13,Products!$A$2:$A$9,Products!$D$2:$D$9,"0")</f>
         <v>0</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="9" t="str">
+      <c r="I13" s="6" t="str">
         <f t="shared" si="1"/>
         <v>Missing Product</v>
       </c>
@@ -1772,7 +1576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D57CAE5C-A4E4-459F-B5C5-5E739F74E4C0}">
   <dimension ref="A3:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
